--- a/forms/trg/Formulir_TRG_ambioc.xlsx
+++ b/forms/trg/Formulir_TRG_ambioc.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B35)</f>
+        <f>COUNTA(Anggota!B5:B36)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F35)</f>
+        <f>COUNTA(Anggota!F5:F36)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Yayu Anugrah La Nafie, M.Sc.</t>
+          <t>Prof. Dr. Nadiarti Nurdin Kadir</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Marine Science, Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Seagrass Bio-Ecology</t>
+          <t>Professor in Aquatic Ecology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,7 +933,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57221441941</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,22 +950,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Dody Priosambodo</t>
+          <t>Dr. Yayu Anugrah La Nafie, M.Sc.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Department of Biology, Hasanuddin University</t>
+          <t>Marine Science, Hasanuddin University</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Invertebrate Biology</t>
+          <t>Specialist in Seagrass Bio-Ecology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,22 +987,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Aidah Ambo Ala Husain</t>
+          <t>Dr. Dody Priosambodo</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Marine Science, Hasanuddin University</t>
+          <t>Department of Biology, Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Expert in Reef Fish Bio-Ecology</t>
+          <t>Specialist in Invertebrate Biology</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,22 +1024,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Abigail Mary Moore</t>
+          <t>Dr. Aidah Ambo Ala Husain</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Graduate School, Universitas Hasanuddin, Makassar City, Indonesia</t>
+          <t>Marine Science, Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Natural Resource Conservation</t>
+          <t>Expert in Reef Fish Bio-Ecology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Widyastuti Umar, S.Kel</t>
+          <t>Dr. Abigail Mary Moore</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Marine Science, Hasanuddin University</t>
+          <t>Graduate School, Universitas Hasanuddin, Makassar City, Indonesia</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Focused on Genetic Population</t>
+          <t>Specialist in Natural Resource Conservation</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,22 +1098,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Mardiana Ethrawaty Fachri</t>
+          <t>Dr. Widyastuti Umar, S.Kel</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Social Economic of Fisheries, Hasanuddin University</t>
+          <t>Marine Science, Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Sociology of Coastal Community</t>
+          <t>Focused on Genetic Population</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1135,22 +1135,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Shannon Switzer Swanson , Ph.D</t>
+          <t>Prof. Dr. Mardiana Ethrawaty Fachri</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>California State University San Marcos, United States</t>
+          <t>Social Economic of Fisheries, Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Expert in Social Ecology, Marine Conservation, Fisheries Management</t>
+          <t>Sociology of Coastal Community</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1172,22 +1172,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Els Lea R De Keyzer, Ph.D</t>
+          <t>Shannon Switzer Swanson , Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Universiteit Antwerpen, Belgium</t>
+          <t>California State University San Marcos, United States</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Evolutionary Genomics · Population Genomics · Fish Evolution · Hybridization · Adaptive Radiation · Metabarcoding · RAD Sequencing</t>
+          <t>Expert in Social Ecology, Marine Conservation, Fisheries Management</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1209,22 +1209,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Amanda Pricella Putri, S.Pi., M.Sc.</t>
+          <t>Els Lea R De Keyzer, Ph.D</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Aquatic Resource Management, Hasanuddin University</t>
+          <t>Universiteit Antwerpen, Belgium</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Marine Conservation, Marine Governance, Interdisciplinary Science</t>
+          <t>Evolutionary Genomics · Population Genomics · Fish Evolution · Hybridization · Adaptive Radiation · Metabarcoding · RAD Sequencing</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Zabhika Dinda Istnaeni, S.Pi., M.Si.</t>
+          <t>Amanda Pricella Putri, S.Pi., M.Sc.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1259,7 +1259,11 @@
           <t>Aquatic Resource Management, Hasanuddin University</t>
         </is>
       </c>
-      <c r="E14" s="11" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Marine Conservation, Marine Governance, Interdisciplinary Science</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1279,15 +1283,19 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dr. Arfiani Rizki Paramata, S.Pi.,M.Si.</t>
+          <t>Zabhika Dinda Istnaeni, S.Pi., M.Si.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Aquatic Resource Management, Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
@@ -1308,12 +1316,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Sutra Nobu</t>
+          <t>Dr. Arfiani Rizki Paramata, S.Pi.,M.Si.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1337,12 +1345,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Samliok Ndobe</t>
+          <t>Sutra Nobu</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1366,12 +1374,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Iqram, PhDcand.</t>
+          <t>Samliok Ndobe</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1395,24 +1403,16 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Fitra Jaya, S.Pi., M.Sc.</t>
+          <t>Muhammad Iqram, PhDcand.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Social Economic of Fisheries, Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Social-Ecological Network Modelling</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="11" t="n"/>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1432,16 +1432,24 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Abdul Gani, S.Pi., M.P</t>
+          <t>Fitra Jaya, S.Pi., M.Sc.</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Social Economic of Fisheries, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Social-Ecological Network Modelling</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
@@ -1461,12 +1469,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>A. Diva Sanni Iftitah</t>
+          <t>Abdul Gani, S.Pi., M.P</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -1490,12 +1498,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Najwa Aulia</t>
+          <t>A. Diva Sanni Iftitah</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
@@ -1519,24 +1527,16 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Dr. Andi Aliah Hidayani, M.Si</t>
+          <t>Najwa Aulia</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Aquaculture, Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Expert in Genetics</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="11" t="n"/>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
@@ -1554,10 +1554,26 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="11" t="n"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Dr. Andi Aliah Hidayani, M.Si</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Aquaculture, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Expert in Genetics</t>
+        </is>
+      </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
@@ -1565,7 +1581,11 @@
       <c r="J24" s="12" t="n"/>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1754,15 +1774,32 @@
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
